--- a/CATI/saved_states/NTC_future_30_day_forecast.xlsx
+++ b/CATI/saved_states/NTC_future_30_day_forecast.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,400 +443,75 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45938</v>
+        <v>46003</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.5231927806974797</v>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45939</v>
+        <v>46006</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.5209804952401893</v>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45940</v>
+        <v>46007</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.5065710867903077</v>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45943</v>
+        <v>46008</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.459651378131932</v>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45944</v>
+        <v>46009</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.5198017535372446</v>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45945</v>
+        <v>46010</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.5116032562466284</v>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45946</v>
+        <v>46013</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.5287654305729264</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.5195674080494872</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>45950</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.512215888081418</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45951</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.5360471902329513</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>45952</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.5025403583806618</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45953</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.4767854127866619</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.5183978312347333</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45957</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.4269467904390964</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45958</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.4101813867302059</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45959</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.3919846809129687</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.3636775275491568</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45961</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.351060180199442</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45964</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.3882488093314399</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.4568353223753209</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.4603106870290017</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.4781550769901902</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45968</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.526668097322183</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45971</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.5238777562366066</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45972</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.5308701187963685</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45973</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.5323325299748323</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>45974</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.5442366414593995</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.5428727786114524</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>45978</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.5368467490246605</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>45979</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.5362065544326973</v>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
   </sheetData>
